--- a/Output/SDTM_Results.xlsx
+++ b/Output/SDTM_Results.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" state="visible" r:id="rId1"/>
@@ -757,70 +757,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="9.90625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="15.26953125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10.36328125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="41" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="16.453125" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="11.54296875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="10.36328125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9.90625" customWidth="1" min="3" max="3"/>
+    <col width="15" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="41" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="22">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>OID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" s="22" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Repeating</t>
         </is>
       </c>
       <c r="C1" s="22" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="D1" s="22" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>IsReferenceData</t>
         </is>
       </c>
       <c r="E1" s="22" t="inlineStr">
         <is>
-          <t>SasDatasetName</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="F1" s="22" t="inlineStr">
         <is>
-          <t>Repeating</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="G1" s="22" t="inlineStr">
-        <is>
-          <t>IsReferenceData</t>
-        </is>
-      </c>
-      <c r="H1" s="22" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I1" s="22" t="inlineStr">
-        <is>
-          <t>ArchiveLocationID</t>
-        </is>
-      </c>
-      <c r="J1" s="22" t="inlineStr">
-        <is>
-          <t>StandardOID</t>
-        </is>
-      </c>
-      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -829,55 +807,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IG.TS</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>Tabulation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tabulation</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>One record per trial summary parameter value</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>One record per trial summary parameter value</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>LF.TS</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>STD.1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
         <is>
           <t>Trial Summary</t>
         </is>
@@ -886,55 +839,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IG.TA</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>Tabulation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tabulation</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>One record per arm and epoch</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>One record per arm and epoch</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>LF.TA</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>STD.1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>Trial Arms</t>
         </is>
@@ -943,55 +871,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IG.TE</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>Tabulation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tabulation</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>One record per element</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>One record per element</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>LF.TE</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>STD.1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>Trial Elements</t>
         </is>
@@ -1000,55 +903,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IG.TV</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Tabulation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tabulation</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>One record per planned visit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>One record per planned visit</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>LF.TV</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>STD.1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
         <is>
           <t>Trial Visits</t>
         </is>
@@ -1057,55 +935,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IG.TI</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Tabulation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tabulation</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>One record per eligibility criterion per study version</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>One record per eligibility criterion per study version</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>LF.TI</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>STD.1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
         <is>
           <t>Trial Inclusion and Exclusion Criteria</t>
         </is>
@@ -1202,12 +1055,12 @@
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Xanomeline High Dose</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>Active Substance</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E2" s="12" t="n">
@@ -1215,15 +1068,19 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>Screening</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
           <t>Screening Element</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Randomized to Placebo TTS (adhesive patches)</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
@@ -1245,12 +1102,12 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Xanomeline High Dose</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Active Substance</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E3" s="12" t="n">
@@ -1258,15 +1115,19 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>High - Start</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr"/>
+          <t>Placebo TTS (adhesive patches)</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
@@ -1288,12 +1149,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Xanomeline High Dose</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Active Substance</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E4" s="12" t="n">
@@ -1301,16 +1162,24 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg + 25 cm2, 27 mg</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>High - Middle</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>Placebo TTS (adhesive patches)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>not willing to do online questionnaire: transition to StudyEpoch_4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Treatment Two</t>
@@ -1330,12 +1199,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Xanomeline High Dose</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Active Substance</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -1343,15 +1212,19 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>High - End</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Placebo TTS (adhesive patches)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
@@ -1372,12 +1245,12 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Xanomeline High Dose</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Active Substance</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -1385,15 +1258,19 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
+          <t>Follow up</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>Follow Up Element</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Follow up</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -1427,15 +1304,19 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
+          <t>Screening</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
           <t>Screening Element</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Randomized to Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -1469,15 +1350,19 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
@@ -1511,23 +1396,31 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
           <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>not willing to do online questionnaire: transition to StudyEpoch_4</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Treatment Two</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="29" customHeight="1">
+    <row r="10" ht="72.5" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>H2Q-MC-LZZT</t>
@@ -1553,15 +1446,19 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
           <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -1595,15 +1492,19 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
+          <t>Follow up</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
           <t>Follow Up Element</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Follow up</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -1624,12 +1525,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Xanomeline High Dose</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Active Substance</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1637,15 +1538,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Screening</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Screening Element</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Randomized to Xanomeline TTS (adhesive patches) 50 cm2, 54 mg Xanomeline TTS (adhesive patches) 50 cm2, 54 mg + 25 cm2, 27 mg Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -1666,12 +1571,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Xanomeline High Dose</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Active Substance</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1679,15 +1584,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Placebo TTS (adhesive patches)</t>
+          <t>High - Start</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Placebo</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
@@ -1708,12 +1617,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Xanomeline High Dose</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Active Substance</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1721,16 +1630,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Placebo TTS (adhesive patches)</t>
+          <t>High - Middle</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Placebo</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg + 25 cm2, 27 mg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>not willing to do online questionnaire: transition to StudyEpoch_4</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Treatment Two</t>
@@ -1750,12 +1667,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Xanomeline High Dose</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Active Substance</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1763,15 +1680,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Placebo TTS (adhesive patches)</t>
+          <t>High - End</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Placebo</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
@@ -1792,12 +1713,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Xanomeline High Dose</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>Active Substance</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1805,15 +1726,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Follow up</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Follow Up Element</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Follow up</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
@@ -5369,7 +5294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="19.7265625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -6868,47 +6793,34 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>XINONILINE50</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>RANDOM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Route of Administration</t>
+          <t>Trial is Randomized</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ORAL</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>C38288</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>http://www.cdisc.org</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6836,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -6958,7 +6870,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//www.cdisc.org</t>
+          <t>http://www.cdisc.org</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6978,34 +6890,47 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C36" t="n">
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SEXPOP</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sex of Participants</t>
+          <t>Route of Administration</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>['Female', 'Male']</t>
+          <t>ORAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>C38288</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>//www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -7032,17 +6957,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SPONSOR</t>
+          <t>SEXPOP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Clinical Study Sponsor; Sponsor; Study Sponsor</t>
+          <t>Sex of Participants</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>['Female', 'Male']</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -7074,37 +6999,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>STYPE</t>
+          <t>SPONSOR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Study Type; Study Type Classification</t>
+          <t>Clinical Study Sponsor; Sponsor; Study Sponsor</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Interventional Study</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>C98388</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>//www.cdisc.org</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -7131,17 +7041,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TBLIND</t>
+          <t>STYPE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Study Blinding Design; Study Blinding Schema; Study Masking Design; Trial Blinding Design; Trial Blinding Schema; Trial Masking Design</t>
+          <t>Study Type; Study Type Classification</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Double Blind Study</t>
+          <t>Interventional Study</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7151,7 +7061,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C15228</t>
+          <t>C98388</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7188,17 +7098,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>THERAREA</t>
+          <t>TBLIND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Therapeutic Area</t>
+          <t>Study Blinding Design; Study Blinding Schema; Study Masking Design; Trial Blinding Design; Trial Blinding Schema; Trial Masking Design</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>"Mild to Moderate Alzheimer's Disease", "Alzheimer's disease"</t>
+          <t>Double Blind Study</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7208,17 +7118,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MILD_MOD_ALZ', '26929004</t>
+          <t>C15228</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SPONSOR', 'SNOMED</t>
+          <t>//www.cdisc.org</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>12', '2025-02-01</t>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -7233,27 +7143,29 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Code_152</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TINDTP</t>
+          <t>THERAREA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trial Intent Type</t>
+          <t>Therapeutic Area</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Treatment Study</t>
+          <t>"Mild to Moderate Alzheimer's Disease", "Alzheimer's disease"</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7263,17 +7175,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C49656</t>
+          <t>MILD_MOD_ALZ', '26929004</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>http://www.cdisc.org</t>
+          <t>SPONSOR', 'SNOMED</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>12', '2025-02-01</t>
         </is>
       </c>
     </row>
@@ -7289,11 +7201,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Code_152_a</t>
+          <t>Code_152</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -7308,7 +7220,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cure Study</t>
+          <t>Treatment Study</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7318,7 +7230,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C49654</t>
+          <t>C49656</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -7343,34 +7255,47 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C43" t="n">
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Code_152_a</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TITLE</t>
+          <t>TINDTP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Official Study Title; Study Title; Trial Title</t>
+          <t>Trial Intent Type</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease</t>
+          <t>Cure Study</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C49654</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -7385,27 +7310,29 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>1</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>XINONILINE50</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TRT</t>
+          <t>TITLE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Investigational Therapy or Treatment</t>
+          <t>Official Study Title; Study Title; Trial Title</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Xinomiline</t>
+          <t>Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7426,11 +7353,11 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>XINONILINE25</t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7466,11 +7393,11 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PLACEBO</t>
+          <t>XINONILINE25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7485,7 +7412,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>Xinomiline</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7506,46 +7433,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Code_153</t>
+          <t>PLACEBO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TTYPE</t>
+          <t>TRT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trial Scope; Trial Type</t>
+          <t>Investigational Therapy or Treatment</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Efficacy Study</t>
+          <t>placebo</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>C49666</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>http://www.cdisc.org</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -7561,11 +7473,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Code_154</t>
+          <t>Code_153</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7580,7 +7492,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Safety Study</t>
+          <t>Efficacy Study</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7590,7 +7502,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C49667</t>
+          <t>C49666</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -7616,44 +7528,99 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Code_154</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TTYPE</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Trial Scope; Trial Type</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Safety Study</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C49667</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
         <v>3</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Code_155</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>TTYPE</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Trial Scope; Trial Type</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Pharmacokinetic Study</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>C49663</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>http://www.cdisc.org</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>2025-09-26</t>
         </is>
@@ -9786,6 +9753,11 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>

--- a/Output/SDTM_Results.xlsx
+++ b/Output/SDTM_Results.xlsx
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2178,7 +2178,7 @@
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2714,12 +2714,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3250,12 +3250,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Active Substance</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">

--- a/Output/SDTM_Results.xlsx
+++ b/Output/SDTM_Results.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-9405" yWindow="-16890" windowWidth="21915" windowHeight="15960" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" state="visible" r:id="rId1"/>
@@ -1748,6 +1748,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -4175,7 +4176,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="29" customHeight="1">
+    <row r="9" ht="43.5" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>H2Q-MC-LZZT</t>
@@ -5285,6 +5286,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
